--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488222_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488222_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8834</v>
+        <v>8.0716</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6584</v>
+        <v>6.7463</v>
       </c>
       <c r="F2" t="n">
-        <v>4.225</v>
+        <v>1.3253</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9938</v>
+        <v>2.6217</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.6545</v>
+        <v>-0.6192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6607</v>
+        <v>3.2409</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.2963</v>
+        <v>2.3804</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.5037</v>
+        <v>-0.2536</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2074</v>
+        <v>2.6341</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3025</v>
+        <v>0.2413</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1508</v>
+        <v>-0.3656</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4533</v>
+        <v>0.6069</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3352</v>
+        <v>2.2234</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5628</v>
+        <v>0.0619</v>
       </c>
       <c r="T2" t="n">
-        <v>3.661</v>
+        <v>-0.0575</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9018</v>
+        <v>0.1194</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8321</v>
+        <v>4.091</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1466</v>
+        <v>5.3498</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2263</v>
+        <v>5.5337</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1473</v>
+        <v>1.0116</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0791</v>
+        <v>4.5222</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6217</v>
+        <v>1.8168</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6192</v>
+        <v>-0.4596</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2409</v>
+        <v>2.2764</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3804</v>
+        <v>0.9456</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2536</v>
+        <v>-0.4858</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6341</v>
+        <v>1.4314</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2413</v>
+        <v>0.8712</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3656</v>
+        <v>0.0262</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6069</v>
+        <v>0.845</v>
       </c>
       <c r="P3" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2234</v>
+        <v>3.1499</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7834</v>
+        <v>0.8652</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6566</v>
+        <v>0.3641</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1269</v>
+        <v>0.5011</v>
       </c>
       <c r="V3" t="n">
-        <v>4.091</v>
+        <v>0.6283</v>
       </c>
       <c r="W3" t="n">
-        <v>5.3498</v>
+        <v>0.6283</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.548</v>
+        <v>5.2661</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8042</v>
+        <v>1.3858</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7438</v>
+        <v>3.8803</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8168</v>
+        <v>-0.9938</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4596</v>
+        <v>-1.6545</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2764</v>
+        <v>0.6607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9456</v>
+        <v>-1.2963</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4858</v>
+        <v>-1.5037</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4314</v>
+        <v>0.2074</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8712</v>
+        <v>0.3025</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0262</v>
+        <v>-0.1508</v>
       </c>
       <c r="O4" t="n">
-        <v>0.845</v>
+        <v>0.4533</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2234</v>
+        <v>1.4823</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1499</v>
+        <v>3.3352</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8794</v>
+        <v>1.9455</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1567</v>
+        <v>1.3884</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7227</v>
+        <v>0.5571</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6283</v>
+        <v>2.8321</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6283</v>
+        <v>3.1466</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9853</v>
+        <v>3.9816</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0241</v>
+        <v>3.0696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.912</v>
       </c>
       <c r="G5" t="n">
         <v>1.6047</v>
@@ -844,13 +844,13 @@
         <v>2.4087</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7491</v>
+        <v>0.2471</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0943</v>
+        <v>-0.0488</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3452</v>
+        <v>0.2959</v>
       </c>
       <c r="V5" t="n">
         <v>1.5738</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0533</v>
+        <v>1.6218</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1903</v>
+        <v>0.0012</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2436</v>
+        <v>1.6206</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1206</v>
+        <v>-2.824</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1021</v>
+        <v>-1.8135</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0185</v>
+        <v>-1.0105</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09719999999999999</v>
+        <v>-1.8828</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0557</v>
+        <v>-2.1008</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0415</v>
+        <v>0.218</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0234</v>
+        <v>-0.9412</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0464</v>
+        <v>0.2873</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.023</v>
+        <v>-1.2285</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3706</v>
+        <v>2.7793</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.7793</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3589</v>
+        <v>1.0371</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3246</v>
+        <v>0.9401</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0343</v>
+        <v>0.097</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9444</v>
+        <v>0.6294</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0.9439</v>
       </c>
       <c r="X6" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7819</v>
+        <v>0.9062</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2724</v>
+        <v>-0.2882</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0543</v>
+        <v>1.1943</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.824</v>
+        <v>0.1206</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8135</v>
+        <v>0.1021</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0105</v>
+        <v>0.0185</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8828</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1008</v>
+        <v>0.0557</v>
       </c>
       <c r="L8" t="n">
-        <v>0.218</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9412</v>
+        <v>0.0234</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2873</v>
+        <v>0.0464</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2285</v>
+        <v>-0.023</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7793</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7793</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1972</v>
+        <v>0.2117</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6666</v>
+        <v>0.2266</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4693</v>
+        <v>-0.0149</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6294</v>
+        <v>0.9444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9439</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3556</v>
+        <v>-0.081</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4811</v>
+        <v>-0.1326</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1255</v>
+        <v>0.0516</v>
       </c>
       <c r="G9" t="n">
         <v>-0.785</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1149</v>
+        <v>0.3895</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>0.1844</v>
       </c>
       <c r="U9" t="n">
-        <v>0.279</v>
+        <v>0.2052</v>
       </c>
       <c r="V9" t="n">
         <v>0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8913</v>
+        <v>-0.4257</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5281</v>
+        <v>-1.1364</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6368</v>
+        <v>0.7107</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0923</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3549</v>
+        <v>0.1107</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3283</v>
+        <v>0.0634</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0266</v>
+        <v>0.0473</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5058</v>
+        <v>-0.5762</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8969</v>
+        <v>-2.0904</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3911</v>
+        <v>1.5142</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9677</v>
@@ -1312,13 +1312,13 @@
         <v>2.594</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2798</v>
+        <v>0.6498</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2561</v>
+        <v>0.5503</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0236</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.0005</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3284</v>
+        <v>-3.4274</v>
       </c>
       <c r="E12" t="n">
-        <v>0.614</v>
+        <v>0.4412</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9425</v>
+        <v>-3.8686</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0788</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8414</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8891</v>
+        <v>0.7163</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0478</v>
+        <v>0.0261</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8321</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8846</v>
+        <v>-3.7167</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3519</v>
+        <v>-3.8392</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4672</v>
+        <v>0.1225</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7779</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7091</v>
+        <v>0.877</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0721</v>
+        <v>0.5848</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6369</v>
+        <v>0.2922</v>
       </c>
       <c r="V13" t="n">
         <v>-0.0011</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.4566</v>
+        <v>18.09810000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4714</v>
+        <v>6.113</v>
       </c>
       <c r="F14" t="n">
         <v>11.9851</v>
@@ -1546,13 +1546,13 @@
         <v>19.4551</v>
       </c>
       <c r="S14" t="n">
-        <v>5.496500000000001</v>
+        <v>7.137899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.270699999999999</v>
+        <v>4.912100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2257</v>
+        <v>2.2259</v>
       </c>
       <c r="V14" t="n">
         <v>8.1807</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2815</v>
+        <v>2.8536</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8262</v>
+        <v>3.1199</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5446</v>
+        <v>-0.2663</v>
       </c>
       <c r="G16" t="n">
         <v>5.8703</v>
@@ -1702,13 +1702,13 @@
         <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9038</v>
+        <v>-0.3317</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.2359</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3741</v>
+        <v>-0.0958</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5733</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2878</v>
+        <v>0.041</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2284</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0594</v>
+        <v>0.041</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3126</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1884</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8758</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1585</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1812</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0226</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4712</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3696</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8984</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.041</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6666</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0794</v>
+        <v>0.041</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0164</v>
+        <v>-0.5614</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.6529</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0164</v>
+        <v>0.0915</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.3126</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.1884</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.8758</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.1585</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.1812</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.4712</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.3696</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.8984</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0164</v>
+        <v>-0.2621</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.2148</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0164</v>
+        <v>-0.0473</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6201</v>
+        <v>-0.5709</v>
       </c>
       <c r="E19" t="n">
         <v>-0.6102</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0394</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8374</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4683</v>
+        <v>-0.4191</v>
       </c>
       <c r="T19" t="n">
         <v>0.0211</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4895</v>
+        <v>-0.4402</v>
       </c>
       <c r="V19" t="n">
         <v>0.315</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9728</v>
+        <v>-1.0467</v>
       </c>
       <c r="E20" t="n">
         <v>-0.2717</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="G20" t="n">
         <v>1.8827</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9297</v>
+        <v>-1.0035</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1766</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7531</v>
+        <v>-0.827</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6289</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0402</v>
+        <v>-1.066</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8062</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.234</v>
+        <v>-0.4556</v>
       </c>
       <c r="G21" t="n">
         <v>0.0471</v>
@@ -2092,13 +2092,13 @@
         <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8852</v>
+        <v>-0.9109</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6354</v>
+        <v>-0.4396</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2497</v>
+        <v>-0.4713</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9433</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2217</v>
+        <v>-2.09</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8473</v>
+        <v>-2.0432</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3744</v>
+        <v>-0.0468</v>
       </c>
       <c r="G22" t="n">
         <v>-1.637</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6223</v>
+        <v>-0.4906</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3084</v>
+        <v>0.1126</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9307</v>
+        <v>-0.6031</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2594</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9983</v>
+        <v>-2.8417</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7178</v>
+        <v>-1.7228</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2805</v>
+        <v>-1.1189</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1803</v>
+        <v>1.4905</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8623</v>
+        <v>1.0051</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.4853</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5578</v>
+        <v>0.7581</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2628</v>
+        <v>-0.7562</v>
       </c>
       <c r="L23" t="n">
-        <v>0.705</v>
+        <v>1.5143</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3774</v>
+        <v>0.7323</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4004</v>
+        <v>1.7613</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.023</v>
+        <v>-1.029</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6676</v>
+        <v>-3.3352</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8529</v>
+        <v>-4.6322</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5215</v>
+        <v>-0.997</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3071</v>
+        <v>-0.3665</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2144</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6289</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4802</v>
+        <v>-3.0476</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0166</v>
+        <v>-2.7178</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4636</v>
+        <v>-0.3298</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4905</v>
+        <v>-0.1803</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0051</v>
+        <v>-0.8623</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4853</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7581</v>
+        <v>-0.5578</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7562</v>
+        <v>-1.2628</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5143</v>
+        <v>0.705</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7323</v>
+        <v>0.3774</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7613</v>
+        <v>0.4004</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.029</v>
+        <v>-0.023</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.3352</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.6322</v>
+        <v>-1.8529</v>
       </c>
       <c r="R24" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6355</v>
+        <v>-0.5708</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6603</v>
+        <v>-0.3071</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9752</v>
+        <v>-0.2636</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W24" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.5177</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9213</v>
+        <v>-4.986</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1529</v>
+        <v>-4.4467</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7683</v>
+        <v>-0.5393</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8118</v>
@@ -2404,13 +2404,13 @@
         <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2049</v>
+        <v>0.1402</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2363</v>
+        <v>-0.0575</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0313</v>
+        <v>0.1977</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5733</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9202</v>
+        <v>-5.6206</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.7492</v>
+        <v>-5.1616</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.171</v>
+        <v>-0.459</v>
       </c>
       <c r="G26" t="n">
         <v>0.1423</v>
@@ -2482,13 +2482,13 @@
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3388</v>
+        <v>-0.0392</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.149</v>
+        <v>-0.5614</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8103</v>
+        <v>0.5223</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2033</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-16.4567</v>
+        <v>-15.8039</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.9849</v>
+        <v>-11.985</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.4716</v>
+        <v>-3.8188</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4114</v>
+        <v>7.411400000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>7.1814</v>
+        <v>7.181399999999998</v>
       </c>
       <c r="I27" t="n">
         <v>0.2300000000000009</v>
@@ -2536,19 +2536,19 @@
         <v>4.662599999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4781999999999995</v>
+        <v>0.4782</v>
       </c>
       <c r="L27" t="n">
         <v>4.184100000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>2.7488</v>
+        <v>2.748800000000001</v>
       </c>
       <c r="N27" t="n">
         <v>6.703000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.954299999999999</v>
+        <v>-3.9543</v>
       </c>
       <c r="P27" t="n">
         <v>-10.1908</v>
@@ -2560,13 +2560,13 @@
         <v>9.264299999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.4966</v>
+        <v>-4.8437</v>
       </c>
       <c r="T27" t="n">
         <v>-2.2257</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.2707</v>
+        <v>-2.617799999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-8.180999999999999</v>
